--- a/ZonasEscolares/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7632,7 +7632,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10648,7 +10648,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10856,7 +10856,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -11012,7 +11012,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11168,7 +11168,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11428,7 +11428,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11532,7 +11532,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11740,7 +11740,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -11948,7 +11948,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12000,7 +12000,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12052,7 +12052,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -12186,7 +12186,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -12260,7 +12260,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12416,7 +12416,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12520,7 +12520,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12676,7 +12676,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12728,7 +12728,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12780,7 +12780,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12832,7 +12832,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -12988,7 +12988,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13092,7 +13092,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13196,7 +13196,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13508,7 +13508,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13560,7 +13560,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13612,7 +13612,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -13642,7 +13642,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -13694,7 +13694,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13716,7 +13716,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13768,7 +13768,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13872,7 +13872,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13924,7 +13924,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -13976,7 +13976,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -14058,7 +14058,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14080,7 +14080,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14236,7 +14236,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -14266,7 +14266,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14444,7 +14444,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14496,7 +14496,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14548,7 +14548,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14600,7 +14600,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14652,7 +14652,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -14682,7 +14682,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14704,7 +14704,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -14734,7 +14734,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -14786,7 +14786,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14808,7 +14808,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14912,7 +14912,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -14942,7 +14942,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14964,7 +14964,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15016,7 +15016,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15224,7 +15224,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -15358,7 +15358,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15432,7 +15432,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -15462,7 +15462,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15536,7 +15536,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15588,7 +15588,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15640,7 +15640,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15692,7 +15692,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -15722,7 +15722,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15744,7 +15744,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15796,7 +15796,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15900,7 +15900,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15952,7 +15952,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16004,7 +16004,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -16034,7 +16034,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16056,7 +16056,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -16086,7 +16086,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -16138,7 +16138,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16160,7 +16160,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16368,7 +16368,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -16398,7 +16398,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16420,7 +16420,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -16502,7 +16502,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -16554,7 +16554,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -16606,7 +16606,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16628,7 +16628,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -16658,7 +16658,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16680,7 +16680,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -16762,7 +16762,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16836,7 +16836,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -16866,7 +16866,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16888,7 +16888,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -16970,7 +16970,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17044,7 +17044,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17096,7 +17096,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -17126,7 +17126,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17148,7 +17148,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>SAN_JUAN_DE_LURIGANCHO</t>
+          <t>SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SAN_JUAN_DE_LURIGANCHO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
